--- a/data/trans_dic/P44A$sangre-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -615,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -625,47 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -678,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 48,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,75; 29,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,54; 98,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 39,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,31; 80,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,77; 30,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,83; 25,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,87; 97,02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -735,47 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -788,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,38; 33,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,0; 19,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,35; 71,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 22,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72,48; 82,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,19; 20,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,43; 15,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,37; 74,83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -845,47 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -898,54 +898,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,98; 35,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,75; 26,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,32; 68,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,09; 28,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,3; 29,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,5; 76,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,46; 25,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,44; 21,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,58; 70,86</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -955,47 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -1008,54 +1008,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 52,73</t>
+          <t>8,13; 41,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 29,59</t>
+          <t>4,72; 25,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,87; 98,34</t>
+          <t>57,93; 73,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,48</t>
+          <t>0,0; 31,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,81</t>
+          <t>0,0; 15,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,96; 80,48</t>
+          <t>50,25; 64,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 32,52</t>
+          <t>6,76; 29,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 26,08</t>
+          <t>3,44; 15,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,26; 97,47</t>
+          <t>56,6; 67,15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1065,47 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -1118,389 +1118,59 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,36; 32,68</t>
+          <t>11,18; 27,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 19,95</t>
+          <t>6,56; 16,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,26; 71,68</t>
+          <t>63,29; 90,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,38</t>
+          <t>3,86; 15,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 23,54</t>
+          <t>3,62; 13,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,12; 82,29</t>
+          <t>67,7; 73,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 21,38</t>
+          <t>9,16; 18,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 15,66</t>
+          <t>6,41; 13,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,19; 74,97</t>
+          <t>67,02; 86,69</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>16,26%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>62,56%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>66,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>5,93; 33,17</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3,55; 27,88</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>56,07; 68,22</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3,06; 29,5</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>3,27; 29,84</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>66,19; 76,53</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>7,5; 24,54</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>5,63; 22,47</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>62,54; 70,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>61,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>8,18; 41,58</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4,89; 26,76</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>58,35; 74,1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 31,4</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 17,18</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,83; 63,99</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 27,43</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2,55; 15,83</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>56,25; 66,92</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>75,84%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>70,7%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>11,08; 28,27</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6,76; 16,74</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>63,62; 89,68</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4,21; 15,61</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3,8; 14,01</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>67,69; 73,86</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,22; 19,08</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6,46; 13,74</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>66,75; 85,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
@@ -1508,11 +1178,8 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1524,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1543,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1634,7 +1301,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1644,47 +1311,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -1697,47 +1364,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52062</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>356261</t>
         </is>
       </c>
     </row>
@@ -1750,54 +1417,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6923</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1003; 8019</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>215045; 327070</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4407</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45972; 57547</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2002; 10509</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1071; 9490</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>274642; 392605</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1807,47 +1474,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>218</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360</t>
         </is>
       </c>
     </row>
@@ -1860,47 +1527,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121375</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239728</t>
         </is>
       </c>
     </row>
@@ -1913,54 +1580,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2118; 13130</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1047; 10459</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>105102; 130251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 8453</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>112916; 128560</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3060; 14912</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3097; 13803</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>225026; 253716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1970,47 +1637,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
     </row>
@@ -2023,47 +1690,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102421</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204922</t>
         </is>
       </c>
     </row>
@@ -2076,54 +1743,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1831; 10740</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1646; 11601</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92267; 112278</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>969; 9008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1029; 9313</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95137; 109511</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4004; 15843</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4088; 16238</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>192059; 217473</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2133,17 +1800,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2158,22 +1825,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -2186,47 +1853,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304199</t>
+          <t>63992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52062</t>
+          <t>62149</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>356261</t>
+          <t>126142</t>
         </is>
       </c>
     </row>
@@ -2239,54 +1906,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>944; 7473</t>
+          <t>2051; 10433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>999; 7926</t>
+          <t>1729; 9382</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>212792; 327645</t>
+          <t>55886; 70855</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6251</t>
+          <t>0; 6628</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4394</t>
+          <t>0; 5592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45718; 57532</t>
+          <t>54157; 69110</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1963; 11277</t>
+          <t>3148; 13817</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1111; 9865</t>
+          <t>2500; 11460</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>272157; 394425</t>
+          <t>115604; 137156</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2296,47 +1963,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>626</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1082</t>
         </is>
       </c>
     </row>
@@ -2349,47 +2016,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118353</t>
+          <t>589045</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>121375</t>
+          <t>338007</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>28799</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>239728</t>
+          <t>927052</t>
         </is>
       </c>
     </row>
@@ -2402,559 +2069,67 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2109; 12856</t>
+          <t>12226; 29752</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1015; 10451</t>
+          <t>10482; 26977</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106769; 131355</t>
+          <t>491588; 699871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5870</t>
+          <t>4125; 16680</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1052; 8908</t>
+          <t>4200; 15993</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>112359; 128204</t>
+          <t>323663; 351987</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2964; 15631</t>
+          <t>19817; 40649</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3106; 14132</t>
+          <t>17675; 38486</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>224415; 254184</t>
+          <t>840970; 1087759</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5201</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>102501</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3879</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4068</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>102421</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8859</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>9269</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>204922</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>1815; 10153</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1559; 12241</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>91869; 111772</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>960; 9257</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1020; 9309</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>94695; 109480</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4647; 15214</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>4230; 16873</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>191920; 217124</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>4476</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>63992</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>62149</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>7388</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5682</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>126142</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2066; 10494</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1788; 9793</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>56294; 71480</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0; 6687</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0; 6194</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>53709; 68973</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3188; 12765</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1850; 11499</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>114887; 136686</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>19647</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>17075</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>589045</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>9152</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>9556</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>338007</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>28799</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>26631</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>927052</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>12122; 30912</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10801; 26726</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>494134; 696550</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>4504; 16699</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>4410; 16270</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>323638; 353144</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>19953; 41268</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>17810; 37903</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>837575; 1075311</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A25:A27"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P44A$sangre-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,85</t>
+          <t>6,52; 49,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 29,94</t>
+          <t>3,69; 32,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,54; 98,17</t>
+          <t>54,94; 74,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,57</t>
+          <t>0,0; 29,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,93</t>
+          <t>0,0; 39,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,31; 80,5</t>
+          <t>63,54; 79,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 30,3</t>
+          <t>5,55; 31,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 25,09</t>
+          <t>2,95; 26,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,87; 97,02</t>
+          <t>60,68; 74,07</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 33,37</t>
+          <t>5,58; 35,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 19,96</t>
+          <t>1,99; 18,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57,35; 71,08</t>
+          <t>58,06; 71,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,47</t>
+          <t>0,0; 13,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,34</t>
+          <t>2,72; 23,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,48; 82,52</t>
+          <t>72,15; 82,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 20,4</t>
+          <t>4,18; 20,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 15,3</t>
+          <t>3,68; 15,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,37; 74,83</t>
+          <t>66,35; 74,96</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 35,08</t>
+          <t>5,77; 33,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 26,42</t>
+          <t>3,52; 27,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,32; 68,53</t>
+          <t>55,83; 68,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 28,7</t>
+          <t>3,05; 27,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 29,86</t>
+          <t>3,31; 29,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,5; 76,55</t>
+          <t>66,61; 77,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 25,55</t>
+          <t>7,58; 24,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 21,62</t>
+          <t>5,86; 22,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,58; 70,86</t>
+          <t>62,68; 70,43</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,83%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 41,34</t>
+          <t>8,12; 37,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 25,64</t>
+          <t>4,73; 24,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,93; 73,45</t>
+          <t>58,94; 73,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,12</t>
+          <t>0,0; 31,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,51</t>
+          <t>0,0; 16,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,25; 64,12</t>
+          <t>51,0; 64,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 29,69</t>
+          <t>7,0; 29,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 15,77</t>
+          <t>3,08; 15,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,6; 67,15</t>
+          <t>56,25; 67,13</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,18; 27,2</t>
+          <t>11,44; 28,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 16,89</t>
+          <t>6,16; 16,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,29; 90,1</t>
+          <t>60,42; 68,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 15,6</t>
+          <t>4,09; 15,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 13,77</t>
+          <t>3,84; 15,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,7; 73,62</t>
+          <t>67,39; 73,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 18,79</t>
+          <t>9,05; 19,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,41; 13,95</t>
+          <t>6,64; 14,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67,02; 86,69</t>
+          <t>64,9; 69,48</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304199</t>
+          <t>61529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52062</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>356261</t>
+          <t>116866</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6923</t>
+          <t>924; 7025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1003; 8019</t>
+          <t>989; 8760</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215045; 327070</t>
+          <t>52194; 70644</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6270</t>
+          <t>0; 6044</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4407</t>
+          <t>0; 4399</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45972; 57547</t>
+          <t>48769; 61219</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2002; 10509</t>
+          <t>1925; 10786</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1071; 9490</t>
+          <t>1114; 9941</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>274642; 392605</t>
+          <t>104218; 127202</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118353</t>
+          <t>124803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>121375</t>
+          <t>135264</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>239728</t>
+          <t>260067</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2118; 13130</t>
+          <t>2196; 13794</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1047; 10459</t>
+          <t>1044; 9549</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105102; 130251</t>
+          <t>112389; 138198</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5223</t>
+          <t>0; 4430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8453</t>
+          <t>1031; 8839</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>112916; 128560</t>
+          <t>125957; 143303</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3060; 14912</t>
+          <t>3054; 15086</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3097; 13803</t>
+          <t>3319; 14066</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>225026; 253716</t>
+          <t>244269; 275967</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102501</t>
+          <t>110413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>102421</t>
+          <t>113242</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>204922</t>
+          <t>223656</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1831; 10740</t>
+          <t>1768; 10178</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1646; 11601</t>
+          <t>1544; 11900</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92267; 112278</t>
+          <t>99162; 120942</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>969; 9008</t>
+          <t>956; 8594</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1029; 9313</t>
+          <t>1034; 9353</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95137; 109511</t>
+          <t>104951; 121395</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4004; 15843</t>
+          <t>4701; 15357</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4088; 16238</t>
+          <t>4403; 16902</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>192059; 217473</t>
+          <t>210073; 236057</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63992</t>
+          <t>69498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62149</t>
+          <t>69058</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>126142</t>
+          <t>138556</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2051; 10433</t>
+          <t>2050; 9497</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1729; 9382</t>
+          <t>1733; 9116</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55886; 70855</t>
+          <t>61716; 77399</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6628</t>
+          <t>0; 6640</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5592</t>
+          <t>0; 5910</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54157; 69110</t>
+          <t>60892; 76986</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3148; 13817</t>
+          <t>3258; 13827</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2500; 11460</t>
+          <t>2239; 11106</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>115604; 137156</t>
+          <t>126051; 150443</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>589045</t>
+          <t>366242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>927052</t>
+          <t>739144</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12226; 29752</t>
+          <t>12508; 30662</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10482; 26977</t>
+          <t>9844; 25970</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>491588; 699871</t>
+          <t>344945; 388744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4125; 16680</t>
+          <t>4369; 16111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4200; 15993</t>
+          <t>4458; 17587</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>323663; 351987</t>
+          <t>356019; 388187</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19817; 40649</t>
+          <t>19570; 42080</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17675; 38486</t>
+          <t>18302; 38607</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840970; 1087759</t>
+          <t>713361; 763640</t>
         </is>
       </c>
     </row>
